--- a/配置表格/L灵根配置表.xlsx
+++ b/配置表格/L灵根配置表.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="linggen_config" sheetId="3" r:id="rId1"/>
     <sheet name="更新说明" sheetId="2" r:id="rId2"/>
+    <sheet name="本轮配置说明" sheetId="4" r:id="rIdConfig4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +53,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -210,8 +211,36 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -404,8 +433,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF17365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF17365D"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -511,8 +562,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -660,13 +725,37 @@
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="9"/>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="10"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="9" xfId="49"/>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="10" xfId="50"/>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="10" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="10" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="38" borderId="10" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="10" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -984,9 +1073,237 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>##var</v>
+      </c>
+      <c r="B1" t="str">
+        <v>linggen_id</v>
+      </c>
+      <c r="C1" t="str">
+        <v>linggen_name</v>
+      </c>
+      <c r="D1" t="str">
+        <v>elements</v>
+      </c>
+      <c r="E1" t="str">
+        <v>color</v>
+      </c>
+      <c r="F1" t="str">
+        <v>icon_id</v>
+      </c>
+      <c r="G1" t="str">
+        <v>tagline</v>
+      </c>
+      <c r="H1" t="str">
+        <v>description</v>
+      </c>
+      <c r="I1" t="str">
+        <v>affinity_modifiers</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>##type</v>
+      </c>
+      <c r="B2" t="str">
+        <v>int</v>
+      </c>
+      <c r="C2" t="str">
+        <v>string</v>
+      </c>
+      <c r="D2" t="str">
+        <v>string</v>
+      </c>
+      <c r="E2" t="str">
+        <v>string</v>
+      </c>
+      <c r="F2" t="str">
+        <v>int?</v>
+      </c>
+      <c r="G2" t="str">
+        <v>string</v>
+      </c>
+      <c r="H2" t="str">
+        <v>string</v>
+      </c>
+      <c r="I2" t="str">
+        <v>string</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>##group</v>
+      </c>
+      <c r="B3"/>
+      <c r="C3" t="str">
+        <v>c</v>
+      </c>
+      <c r="D3" t="str">
+        <v>c</v>
+      </c>
+      <c r="E3" t="str">
+        <v>c</v>
+      </c>
+      <c r="F3" t="str">
+        <v>c</v>
+      </c>
+      <c r="G3" t="str">
+        <v>c</v>
+      </c>
+      <c r="H3" t="str">
+        <v>c</v>
+      </c>
+      <c r="I3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>##</v>
+      </c>
+      <c r="B4" t="str">
+        <v>灵根ID</v>
+      </c>
+      <c r="C4" t="str">
+        <v>灵根名称</v>
+      </c>
+      <c r="D4" t="str">
+        <v>标准行道</v>
+      </c>
+      <c r="E4" t="str">
+        <v>颜色</v>
+      </c>
+      <c r="F4" t="str">
+        <v>图标ID</v>
+      </c>
+      <c r="G4" t="str">
+        <v>简述</v>
+      </c>
+      <c r="H4" t="str">
+        <v>完整说明</v>
+      </c>
+      <c r="I4" t="str">
+        <v>修正项（未开放，留空）</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5"/>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="str">
+        <v>金灵根</v>
+      </c>
+      <c r="D5" t="str">
+        <v>金</v>
+      </c>
+      <c r="E5" t="str">
+        <v>白色</v>
+      </c>
+      <c r="F5"/>
+      <c r="G5" t="str">
+        <v>较易感知收束与分判的标准行道</v>
+      </c>
+      <c r="H5" t="str">
+        <v>先天更易读取、留存与调用金行灵气；收束与分判是主要倾向。其他四类结构功能仍在，不形成职业、堂口或功法锁；数值修正待统一系统接入。</v>
+      </c>
+      <c r="I5"/>
+    </row>
+    <row r="6">
+      <c r="A6"/>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="str">
+        <v>木灵根</v>
+      </c>
+      <c r="D6" t="str">
+        <v>木</v>
+      </c>
+      <c r="E6" t="str">
+        <v>绿色</v>
+      </c>
+      <c r="F6"/>
+      <c r="G6" t="str">
+        <v>较易感知生长与延展的标准行道</v>
+      </c>
+      <c r="H6" t="str">
+        <v>先天更易读取、留存与调用木行灵气；生长与延展是主要倾向。其他四类结构功能仍在，不形成职业、堂口或功法锁；数值修正待统一系统接入。</v>
+      </c>
+      <c r="I6"/>
+    </row>
+    <row r="7">
+      <c r="A7"/>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="str">
+        <v>水灵根</v>
+      </c>
+      <c r="D7" t="str">
+        <v>水</v>
+      </c>
+      <c r="E7" t="str">
+        <v>蓝色</v>
+      </c>
+      <c r="F7"/>
+      <c r="G7" t="str">
+        <v>较易感知流动与渗透的标准行道</v>
+      </c>
+      <c r="H7" t="str">
+        <v>先天更易读取、留存与调用水行灵气；流动与渗透是主要倾向。其他四类结构功能仍在，不形成职业、堂口或功法锁；数值修正待统一系统接入。</v>
+      </c>
+      <c r="I7"/>
+    </row>
+    <row r="8">
+      <c r="A8"/>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="str">
+        <v>火灵根</v>
+      </c>
+      <c r="D8" t="str">
+        <v>火</v>
+      </c>
+      <c r="E8" t="str">
+        <v>红色</v>
+      </c>
+      <c r="F8"/>
+      <c r="G8" t="str">
+        <v>较易感知交换与转化的标准行道</v>
+      </c>
+      <c r="H8" t="str">
+        <v>先天更易读取、留存与调用火行灵气；交换与转化是主要倾向。其他四类结构功能仍在，不形成职业、堂口或功法锁；数值修正待统一系统接入。</v>
+      </c>
+      <c r="I8"/>
+    </row>
+    <row r="9">
+      <c r="A9"/>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="str">
+        <v>土灵根</v>
+      </c>
+      <c r="D9" t="str">
+        <v>土</v>
+      </c>
+      <c r="E9" t="str">
+        <v>黄色</v>
+      </c>
+      <c r="F9"/>
+      <c r="G9" t="str">
+        <v>较易感知承载与稳定的标准行道</v>
+      </c>
+      <c r="H9" t="str">
+        <v>先天更易读取、留存与调用土行灵气；承载与稳定是主要倾向。其他四类结构功能仍在，不形成职业、堂口或功法锁；数值修正待统一系统接入。</v>
+      </c>
+      <c r="I9"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1151,4 +1468,59 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="64" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="40" customHeight="1">
+      <x:c r="A1" s="11" t="str">
+        <x:v>项目</x:v>
+      </x:c>
+      <x:c r="B1" s="11" t="str">
+        <x:v>说明</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="28" customHeight="1">
+      <x:c r="A2" s="9" t="str">
+        <x:v>状态</x:v>
+      </x:c>
+      <x:c r="B2" s="9" t="str">
+        <x:v>完整内容草案，待用户审核；数值可调；非上线验收</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="233" customHeight="1">
+      <x:c r="A3" s="9" t="str">
+        <x:v>本轮工作</x:v>
+      </x:c>
+      <x:c r="B3" s="9" t="str">
+        <x:v>源linggen_config整页为空、无表头且__tables__未登记。本轮按正式P15及最新创角交互案建立九列展示定义，补金、木、水、火、土五条基本灵根：1–5稳定ID、元素、色彩、简述和完整说明。五行语义分别收束分判、生长延展、流动渗透、交换转化、承载稳定；均不锁职业/堂口/功法，不声称其他四行绝对不可用。
+没有扩变异灵根、纯度、多灵根或伪随机候选。最新创角交互案明确玩家明选，P15旧稿中的选择方式待定不能反向覆盖这个确认；本轮五条作为可选内容草案。修正项affinity_modifiers留空，不用猜的百分比把展示稿伪装成已开放的五行战斗机制。
+这是明确的配置内容与schema提案，不声称Luban已导出：需要__tables__登记、记录类型、客户端/服务端读入、创建存档linggen_id和UI资源，再由属性方案定义真实修正结构。图标为空属于资源需求，颜色仅展示映射，不表示品质高低。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="28" customHeight="1">
+      <x:c r="A4" s="9" t="str">
+        <x:v>交付边界</x:v>
+      </x:c>
+      <x:c r="B4" s="9" t="str">
+        <x:v>源文件未改；坐标/资源/程序挂接按需求清单另验收</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="28" customHeight="1">
+      <x:c r="A5" s="9" t="str">
+        <x:v>详细说明</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>世界10_灵根展示定义及接入需求.md</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>